--- a/Dados-iniciais/_Muni_por_Macro_DRS_CIR.xlsx
+++ b/Dados-iniciais/_Muni_por_Macro_DRS_CIR.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="750">
   <si>
-    <t xml:space="preserve">NOME_MUNI</t>
+    <t xml:space="preserve">MUNI_NOME</t>
   </si>
   <si>
     <t xml:space="preserve">MACRO_CODIGO</t>
